--- a/assets/model_input_template.xlsx
+++ b/assets/model_input_template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelInput" sheetId="1" r:id="Rf5da8c37251249a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelInput" sheetId="1" r:id="Rea7f31caff684e01"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -361,7 +361,6 @@
       <x:c r="X1" s="3" t="str">
         <x:v>cua_utility_b</x:v>
       </x:c>
-      <x:c r="Y1" s="4"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="4" t="str">
@@ -436,7 +435,6 @@
       <x:c r="X2" s="4" t="str">
         <x:v>0.8|0.45|0</x:v>
       </x:c>
-      <x:c r="Y2" s="4"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/assets/model_input_template.xlsx
+++ b/assets/model_input_template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelInput" sheetId="1" r:id="Rea7f31caff684e01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelInput" sheetId="1" r:id="Redb9833aecc34160"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -266,26 +266,25 @@
     <x:col min="2" max="2" width="11.220000267028809" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="9.4399995803833" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="9.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="7.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="8.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="11.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="9.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16.440000534057617" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="8.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="19" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="14.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="20.889999389648438" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="10.779999732971191" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="10.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="12.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="13" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="9.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="10.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="9.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="8.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="19" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="20.889999389648438" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="10.779999732971191" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="10.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="12.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="13" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="9.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="10.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="10.329999923706055" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="10.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="10.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="10.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="10.4399995803833" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -302,63 +301,60 @@
         <x:v>strategy_b</x:v>
       </x:c>
       <x:c r="E1" s="3" t="str">
-        <x:v>perspective</x:v>
+        <x:v>currency</x:v>
       </x:c>
       <x:c r="F1" s="3" t="str">
-        <x:v>currency</x:v>
+        <x:v>price_year</x:v>
       </x:c>
       <x:c r="G1" s="3" t="str">
-        <x:v>price_year</x:v>
+        <x:v>horizon_years</x:v>
       </x:c>
       <x:c r="H1" s="3" t="str">
-        <x:v>horizon_years</x:v>
+        <x:v>cycle_years</x:v>
       </x:c>
       <x:c r="I1" s="3" t="str">
-        <x:v>cycle_years</x:v>
+        <x:v>cost_discount_rate</x:v>
       </x:c>
       <x:c r="J1" s="3" t="str">
-        <x:v>cost_discount_rate</x:v>
+        <x:v>effect_discount_rate</x:v>
       </x:c>
       <x:c r="K1" s="3" t="str">
-        <x:v>effect_discount_rate</x:v>
+        <x:v>effect_unit</x:v>
       </x:c>
       <x:c r="L1" s="3" t="str">
-        <x:v>effect_unit</x:v>
+        <x:v>states</x:v>
       </x:c>
       <x:c r="M1" s="3" t="str">
-        <x:v>states</x:v>
+        <x:v>initial_distribution</x:v>
       </x:c>
       <x:c r="N1" s="3" t="str">
-        <x:v>initial_distribution</x:v>
+        <x:v>transition_matrix</x:v>
       </x:c>
       <x:c r="O1" s="3" t="str">
-        <x:v>transition_matrix</x:v>
+        <x:v>initial_cost_a</x:v>
       </x:c>
       <x:c r="P1" s="3" t="str">
-        <x:v>initial_cost_a</x:v>
+        <x:v>initial_cost_b</x:v>
       </x:c>
       <x:c r="Q1" s="3" t="str">
-        <x:v>initial_cost_b</x:v>
+        <x:v>strategy_cost_a</x:v>
       </x:c>
       <x:c r="R1" s="3" t="str">
-        <x:v>strategy_cost_a</x:v>
+        <x:v>strategy_cost_b</x:v>
       </x:c>
       <x:c r="S1" s="3" t="str">
-        <x:v>strategy_cost_b</x:v>
+        <x:v>state_costs</x:v>
       </x:c>
       <x:c r="T1" s="3" t="str">
-        <x:v>state_costs</x:v>
+        <x:v>cea_effect_a</x:v>
       </x:c>
       <x:c r="U1" s="3" t="str">
-        <x:v>cea_effect_a</x:v>
+        <x:v>cea_effect_b</x:v>
       </x:c>
       <x:c r="V1" s="3" t="str">
-        <x:v>cea_effect_b</x:v>
+        <x:v>cua_utility_a</x:v>
       </x:c>
       <x:c r="W1" s="3" t="str">
-        <x:v>cua_utility_a</x:v>
-      </x:c>
-      <x:c r="X1" s="3" t="str">
         <x:v>cua_utility_b</x:v>
       </x:c>
     </x:row>
@@ -376,63 +372,60 @@
         <x:v>Treatment B</x:v>
       </x:c>
       <x:c r="E2" s="4" t="str">
-        <x:v>Healthcare system</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="str">
         <x:v>CNY</x:v>
       </x:c>
+      <x:c r="F2" s="4" t="n">
+        <x:v>2026</x:v>
+      </x:c>
       <x:c r="G2" s="4" t="n">
-        <x:v>2026</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H2" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I2" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J2" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K2" s="4" t="n">
-        <x:v>0</x:v>
+      <x:c r="K2" s="4" t="str">
+        <x:v>life-years</x:v>
       </x:c>
       <x:c r="L2" s="4" t="str">
-        <x:v>life-years</x:v>
+        <x:v>Stable|Progression|Death</x:v>
       </x:c>
       <x:c r="M2" s="4" t="str">
-        <x:v>Stable|Progression|Death</x:v>
+        <x:v>1|0|0</x:v>
       </x:c>
       <x:c r="N2" s="4" t="str">
-        <x:v>1|0|0</x:v>
-      </x:c>
-      <x:c r="O2" s="4" t="str">
         <x:v>0.8,0.15,0.05;0,0.9,0.1;0,0,1</x:v>
       </x:c>
+      <x:c r="O2" s="4" t="n">
+        <x:v>10000</x:v>
+      </x:c>
       <x:c r="P2" s="4" t="n">
-        <x:v>10000</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="Q2" s="4" t="n">
-        <x:v>8000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="R2" s="4" t="n">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="S2" s="4" t="n">
         <x:v>300</x:v>
       </x:c>
+      <x:c r="S2" s="4" t="str">
+        <x:v>2000|5000|0</x:v>
+      </x:c>
       <x:c r="T2" s="4" t="str">
-        <x:v>2000|5000|0</x:v>
+        <x:v>1|0.75|0</x:v>
       </x:c>
       <x:c r="U2" s="4" t="str">
-        <x:v>1|0.75|0</x:v>
+        <x:v>0.9|0.65|0</x:v>
       </x:c>
       <x:c r="V2" s="4" t="str">
-        <x:v>0.9|0.65|0</x:v>
+        <x:v>0.9|0.5|0</x:v>
       </x:c>
       <x:c r="W2" s="4" t="str">
-        <x:v>0.9|0.5|0</x:v>
-      </x:c>
-      <x:c r="X2" s="4" t="str">
         <x:v>0.8|0.45|0</x:v>
       </x:c>
     </x:row>
